--- a/IM/202603_Service_Count_Report.xlsx
+++ b/IM/202603_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$31</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="152">
   <si>
     <t>服務次數統計表        篩選月份：202603</t>
   </si>
@@ -182,6 +182,131 @@
     <t>Pm 冠驅動 掃描 網路線異常</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>THILF02302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區大同南路69號</t>
+  </si>
+  <si>
+    <t>三重重安店</t>
+  </si>
+  <si>
+    <t>裝潢撤店</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:22:00</t>
+  </si>
+  <si>
+    <t>THILF02321</t>
+  </si>
+  <si>
+    <t>新北市三重區大同南路153,153-1號</t>
+  </si>
+  <si>
+    <t>三重同安店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002765</t>
+  </si>
+  <si>
+    <t>15:25:00</t>
+  </si>
+  <si>
+    <t>15:46:00</t>
+  </si>
+  <si>
+    <t>THILF04134</t>
+  </si>
+  <si>
+    <t>新北市三重區大同南路148號1樓</t>
+  </si>
+  <si>
+    <t>三重大同南</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002790</t>
+  </si>
+  <si>
+    <t>吳宗鴻</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>14:31:00</t>
+  </si>
+  <si>
+    <t>T301800172</t>
+  </si>
+  <si>
+    <t>eS-3018A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智基科技開發股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市淡水區中山路123號3樓(淡水分校)</t>
+  </si>
+  <si>
+    <t>淡水</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>T302800006</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信宇顧問有限公司 </t>
+  </si>
+  <si>
+    <t>新北市淡水區民族路50巷46號3樓</t>
+  </si>
+  <si>
+    <t>PM抄表
+送黑色碳粉 1
+清除定著組及上熱組</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>14:17:00</t>
+  </si>
+  <si>
+    <t>T351500137</t>
+  </si>
+  <si>
+    <t>eS-3515AC 彩色複合機</t>
+  </si>
+  <si>
+    <t>華南永昌綜合証券股份有限公司-淡水?</t>
+  </si>
+  <si>
+    <t>新北市淡水區中正路28號4樓(淡水)</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
@@ -203,7 +328,28 @@
     <t>pm</t>
   </si>
   <si>
-    <t>09:30:00</t>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>T252000143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全聯有線電視股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市蘆洲區三民路128巷87-6號2樓(工程部</t>
+  </si>
+  <si>
+    <t>工程部1</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>白線 清潔雷射頭</t>
   </si>
   <si>
     <t>T351800045</t>
@@ -221,15 +367,27 @@
     <t>五股生鮮物流</t>
   </si>
   <si>
+    <t>T352800011</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全聯實業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市蘆洲區水湳街74號2樓</t>
+  </si>
+  <si>
+    <t>蘆洲北二處</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
     <t>T352800031</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t>新北市五股區工商路128號1樓(五股DC廠工商運輸)</t>
   </si>
   <si>
@@ -239,9 +397,6 @@
     <t>11:00:00</t>
   </si>
   <si>
-    <t>維修</t>
-  </si>
-  <si>
     <t>髒汙 更換上熱</t>
   </si>
   <si>
@@ -251,9 +406,6 @@
     <t>THILF02325</t>
   </si>
   <si>
-    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
-  </si>
-  <si>
     <t>新北市五股區西雲路1號</t>
   </si>
   <si>
@@ -263,6 +415,45 @@
     <t>PMQ1 7210002826 L90</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>16:50:00</t>
+  </si>
+  <si>
+    <t>THILF03851</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路510號</t>
+  </si>
+  <si>
+    <t>新莊輔園店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210003057</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>THILF04163</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>新北市新莊區中誠街161號及163號一樓全部</t>
+  </si>
+  <si>
+    <t>新莊中泉店</t>
+  </si>
+  <si>
+    <t>清潔發票機 重接排線</t>
+  </si>
+  <si>
     <t>11:40:00</t>
   </si>
   <si>
@@ -276,6 +467,24 @@
   </si>
   <si>
     <t>PMQ1 7210002834 L90</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>12:10:00</t>
+  </si>
+  <si>
+    <t>THILF04819</t>
+  </si>
+  <si>
+    <t>新北市五股區凌雲路三段46號</t>
+  </si>
+  <si>
+    <t>五股凌雲店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002835 L90</t>
   </si>
   <si>
     <t>合計</t>
@@ -692,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1128,7 +1337,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026030010</v>
+        <v>2026030300</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1137,28 +1346,24 @@
         <v>29</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>54</v>
@@ -1170,16 +1375,14 @@
         <v>40</v>
       </c>
       <c r="P7" s="7"/>
-      <c r="Q7" s="7">
-        <v>335</v>
-      </c>
+      <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>2883</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
@@ -1200,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026030011</v>
+        <v>2026030328</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1209,66 +1412,66 @@
         <v>29</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="M8" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P8" s="3"/>
-      <c r="Q8" s="3">
-        <v>335</v>
-      </c>
+      <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>2883</v>
-      </c>
-      <c r="S8" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
+      <c r="Y8" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z8" s="6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB8" s="3"/>
+      <c r="AB8" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026030082</v>
+        <v>2026030316</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1277,34 +1480,30 @@
         <v>29</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>40</v>
@@ -1312,7 +1511,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>119830</v>
+        <v>0</v>
       </c>
       <c r="S9" s="7" t="s">
         <v>41</v>
@@ -1322,19 +1521,25 @@
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="Y9" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
+        <v>68</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026030083</v>
+        <v>2026030137</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1343,44 +1548,46 @@
         <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>119830</v>
-      </c>
-      <c r="S10" s="3"/>
+        <v>26945</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1388,19 +1595,21 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB10" s="3"/>
+      <c r="AB10" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="7">
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026030084</v>
+        <v>2026030138</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1409,46 +1618,44 @@
         <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>26945</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -1456,9 +1663,11 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA11" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB11" s="7"/>
     </row>
     <row r="12" spans="1:28">
@@ -1466,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026030085</v>
+        <v>2026030100</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1475,42 +1684,40 @@
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>67</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
         <v>43</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>130600</v>
+        <v>33400</v>
       </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -1520,19 +1727,21 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB12" s="3"/>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="7">
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026030086</v>
+        <v>2026030099</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1541,44 +1750,44 @@
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>67</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S13" s="7"/>
+        <v>33400</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -1586,7 +1795,7 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
@@ -1598,7 +1807,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026030090</v>
+        <v>2026030128</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1607,38 +1816,44 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L14" s="6" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="3">
+        <v>2829</v>
+      </c>
       <c r="R14" s="3">
-        <v>0</v>
+        <v>347619</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>41</v>
@@ -1648,11 +1863,9 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -1666,7 +1879,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026030092</v>
+        <v>2026030129</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1675,92 +1888,1104 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L15" s="8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="Q15" s="7">
+        <v>2829</v>
+      </c>
       <c r="R15" s="7">
-        <v>0</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>347619</v>
+      </c>
+      <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB15" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB15" s="7"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>5</v>
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2026030010</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3">
+        <v>335</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2883</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
+      <c r="A17" s="7">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2026030011</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7">
+        <v>335</v>
+      </c>
+      <c r="R17" s="7">
+        <v>2883</v>
+      </c>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB17" s="7"/>
+    </row>
+    <row r="18" spans="1:28">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2026030118</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3">
+        <v>9357</v>
+      </c>
+      <c r="R18" s="3">
+        <v>14126</v>
+      </c>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" s="7">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7">
+        <v>2026030082</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7">
+        <v>119830</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+    </row>
+    <row r="20" spans="1:28">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2026030083</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3">
+        <v>119830</v>
+      </c>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB20" s="3"/>
+    </row>
+    <row r="21" spans="1:28">
+      <c r="A21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7">
+        <v>2026030131</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7">
+        <v>23535</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA21" s="7"/>
+      <c r="AB21" s="7"/>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2026030132</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3">
+        <v>23535</v>
+      </c>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22" s="3"/>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" s="7">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2026030084</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2026030085</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3">
+        <v>130600</v>
+      </c>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24" s="3"/>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" s="7">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7">
+        <v>2026030086</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB25" s="7"/>
+    </row>
+    <row r="26" spans="1:28">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2026030090</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28">
+      <c r="A27" s="7">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2026030344</v>
+      </c>
+      <c r="C27" s="7">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7">
+        <v>0</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z27" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB27" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2026030002</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28">
+      <c r="A29" s="7">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7">
+        <v>2026030092</v>
+      </c>
+      <c r="C29" s="7">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7">
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB29" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2026030094</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="10"/>
+      <c r="AA31" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202603_Service_Count_Report.xlsx
+++ b/IM/202603_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$58</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="219">
   <si>
     <t>服務次數統計表        篩選月份：202603</t>
   </si>
@@ -164,6 +164,21 @@
     <t>抄表</t>
   </si>
   <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>09:38:00</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>更改分享器 Ip重設 重抓驅動掃描</t>
+  </si>
+  <si>
     <t>10:20:00</t>
   </si>
   <si>
@@ -182,6 +197,45 @@
     <t>Pm 冠驅動 掃描 網路線異常</t>
   </si>
   <si>
+    <t>10:40:00</t>
+  </si>
+  <si>
+    <t>T301800079</t>
+  </si>
+  <si>
+    <t>eS-3018A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虹揚印刷股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號9樓之7</t>
+  </si>
+  <si>
+    <t>9F</t>
+  </si>
+  <si>
+    <t>Pm K要補</t>
+  </si>
+  <si>
+    <t>11:04:00</t>
+  </si>
+  <si>
+    <t>T302800122</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號6樓</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
+    <t>列印教學</t>
+  </si>
+  <si>
     <t>14:30:00</t>
   </si>
   <si>
@@ -221,6 +275,24 @@
     <t>PMQ1 7210002765</t>
   </si>
   <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>THILF03318</t>
+  </si>
+  <si>
+    <t>新北市中和區自治街38號及40號</t>
+  </si>
+  <si>
+    <t>中和自治店</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L90</t>
+  </si>
+  <si>
     <t>15:25:00</t>
   </si>
   <si>
@@ -239,9 +311,60 @@
     <t>PMQ1 7210002790</t>
   </si>
   <si>
+    <t>11:13:00</t>
+  </si>
+  <si>
+    <t>11:31:00</t>
+  </si>
+  <si>
+    <t>THILF04748</t>
+  </si>
+  <si>
+    <t>新北市中和區民德路163、165、167、169號</t>
+  </si>
+  <si>
+    <t>中和霸氣店</t>
+  </si>
+  <si>
+    <t>09:50:00</t>
+  </si>
+  <si>
+    <t>10:09:00</t>
+  </si>
+  <si>
+    <t>THILF0C192</t>
+  </si>
+  <si>
+    <t>新北市中和區莊敬路29號</t>
+  </si>
+  <si>
+    <t>北縣福美店</t>
+  </si>
+  <si>
     <t>吳宗鴻</t>
   </si>
   <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>15:38:00</t>
+  </si>
+  <si>
+    <t>T301800078</t>
+  </si>
+  <si>
+    <t>合作金庫商業銀行股份有限公司長庚分公司</t>
+  </si>
+  <si>
+    <t>桃園市龜山區復興街5號(林口長庚分行)</t>
+  </si>
+  <si>
+    <t>林口長庚分行</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
     <t>14:16:00</t>
   </si>
   <si>
@@ -251,9 +374,6 @@
     <t>T301800172</t>
   </si>
   <si>
-    <t>eS-3018A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">智基科技開發股份有限公司 </t>
   </si>
   <si>
@@ -263,9 +383,6 @@
     <t>淡水</t>
   </si>
   <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
     <t>09:30:00</t>
   </si>
   <si>
@@ -273,9 +390,6 @@
   </si>
   <si>
     <t>T302800006</t>
-  </si>
-  <si>
-    <t>eS-3028A 黑白複合機</t>
   </si>
   <si>
     <t xml:space="preserve">信宇顧問有限公司 </t>
@@ -289,6 +403,15 @@
 清除定著組及上熱組</t>
   </si>
   <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>T302800131</t>
+  </si>
+  <si>
     <t>13:30:00</t>
   </si>
   <si>
@@ -307,15 +430,34 @@
     <t>新北市淡水區中正路28號4樓(淡水)</t>
   </si>
   <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>THILF05251</t>
+  </si>
+  <si>
+    <t>桃園市龜山區文化一路259號</t>
+  </si>
+  <si>
+    <t>龜山明德樓</t>
+  </si>
+  <si>
+    <t>TM換機
+Tx800改至UPOS</t>
+  </si>
+  <si>
+    <t>14:05:00</t>
+  </si>
+  <si>
+    <t>PMQ1 L90</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
     <t>08:30:00</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
     <t>T252000136</t>
   </si>
   <si>
@@ -346,12 +488,36 @@
     <t>工程部1</t>
   </si>
   <si>
-    <t>維修</t>
-  </si>
-  <si>
     <t>白線 清潔雷射頭</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>T301800171</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正區336-1號(新莊)</t>
+  </si>
+  <si>
+    <t>新莊</t>
+  </si>
+  <si>
+    <t>T301800174</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路1段10號5樓(板橋分校)</t>
+  </si>
+  <si>
+    <t>板橋</t>
+  </si>
+  <si>
+    <t>T302800123</t>
+  </si>
+  <si>
+    <t>新北市三重區正義北路218號(三重分校)</t>
+  </si>
+  <si>
     <t>T351800045</t>
   </si>
   <si>
@@ -382,7 +548,28 @@
     <t>蘆洲北二處</t>
   </si>
   <si>
-    <t>10:00:00</t>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>T352800029</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號4樓(五股)</t>
+  </si>
+  <si>
+    <t>五股4樓</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>T352800030</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股檢品)</t>
+  </si>
+  <si>
+    <t>五股檢品</t>
   </si>
   <si>
     <t>T352800031</t>
@@ -394,12 +581,18 @@
     <t>五股DC廠工商運輸</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>髒汙 更換上熱</t>
   </si>
   <si>
+    <t>T352800032</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股運輸)</t>
+  </si>
+  <si>
+    <t>五股運輸</t>
+  </si>
+  <si>
     <t>11:20:00</t>
   </si>
   <si>
@@ -415,6 +608,29 @@
     <t>PMQ1 7210002826 L90</t>
   </si>
   <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>THILF02749</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>新北市淡水區淡金路5段20-22號</t>
+  </si>
+  <si>
+    <t>淡水灰瑤子</t>
+  </si>
+  <si>
+    <t>更換手持
+換上8119013772
+換下8119007469</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -433,18 +649,9 @@
     <t>PMQ1 7210003057</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
     <t>THILF04163</t>
   </si>
   <si>
-    <t>一般件</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
     <t>新北市新莊區中誠街161號及163號一樓全部</t>
   </si>
   <si>
@@ -452,9 +659,6 @@
   </si>
   <si>
     <t>清潔發票機 重接排線</t>
-  </si>
-  <si>
-    <t>11:40:00</t>
   </si>
   <si>
     <t>THILF04801</t>
@@ -901,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1197,7 +1401,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026030080</v>
+        <v>2026030325</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1209,16 +1413,16 @@
         <v>30</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>35</v>
@@ -1230,24 +1434,22 @@
         <v>37</v>
       </c>
       <c r="M5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7">
-        <v>914</v>
+        <v>3664</v>
       </c>
       <c r="R5" s="7">
-        <v>1163</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>16787</v>
+      </c>
+      <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -1255,7 +1457,7 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA5" s="7" t="s">
         <v>41</v>
@@ -1269,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026030081</v>
+        <v>2026030080</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1284,13 +1486,13 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>35</v>
@@ -1302,13 +1504,13 @@
         <v>37</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3">
@@ -1317,7 +1519,9 @@
       <c r="R6" s="3">
         <v>1163</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1325,19 +1529,21 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AA6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB6" s="3"/>
+      <c r="AB6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026030300</v>
+        <v>2026030081</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1352,58 +1558,60 @@
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="O7" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+      <c r="Q7" s="7">
+        <v>914</v>
+      </c>
       <c r="R7" s="7">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="S7" s="7"/>
-      <c r="T7" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB7" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB7" s="7"/>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026030328</v>
+        <v>2026030436</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1415,27 +1623,31 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="M8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="6" t="s">
+      <c r="N8" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>40</v>
@@ -1443,7 +1655,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>282084</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>41</v>
@@ -1453,11 +1665,9 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>41</v>
@@ -1471,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026030316</v>
+        <v>2026030437</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1483,63 +1693,61 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+        <v>56</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L9" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>282084</v>
+      </c>
+      <c r="S9" s="7"/>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y9" s="7"/>
       <c r="Z9" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AA9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB9" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB9" s="7"/>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026030137</v>
+        <v>2026030443</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1548,34 +1756,34 @@
         <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>40</v>
@@ -1583,7 +1791,7 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>26945</v>
+        <v>31261</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>41</v>
@@ -1595,7 +1803,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>41</v>
@@ -1609,7 +1817,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026030138</v>
+        <v>2026030444</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1618,34 +1826,34 @@
         <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>43</v>
@@ -1653,7 +1861,7 @@
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>26945</v>
+        <v>31261</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -1663,7 +1871,7 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>41</v>
@@ -1675,7 +1883,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026030100</v>
+        <v>2026030300</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1684,50 +1892,50 @@
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
       <c r="L12" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="N12" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="O12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>33400</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="T12" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
@@ -1741,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026030099</v>
+        <v>2026030328</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1750,40 +1958,38 @@
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="N13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>33400</v>
+        <v>0</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>41</v>
@@ -1793,21 +1999,25 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
+      <c r="Y13" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z13" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB13" s="7"/>
+      <c r="AB13" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026030128</v>
+        <v>2026030460</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1816,44 +2026,38 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3">
-        <v>2829</v>
-      </c>
+      <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>347619</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>41</v>
@@ -1865,7 +2069,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -1879,7 +2083,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026030129</v>
+        <v>2026030316</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1888,66 +2092,66 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>90</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7">
-        <v>2829</v>
-      </c>
+      <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>347619</v>
-      </c>
-      <c r="S15" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="Y15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z15" s="8" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB15" s="7"/>
+      <c r="AB15" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026030010</v>
+        <v>2026030450</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1956,44 +2160,38 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="6" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="3"/>
-      <c r="Q16" s="3">
-        <v>335</v>
-      </c>
+      <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>2883</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>41</v>
@@ -2005,7 +2203,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
@@ -2019,7 +2217,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026030011</v>
+        <v>2026030423</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2028,46 +2226,42 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7">
-        <v>335</v>
-      </c>
+      <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>2883</v>
-      </c>
-      <c r="S17" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -2075,19 +2269,21 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB17" s="7"/>
+      <c r="AB17" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026030118</v>
+        <v>2026030516</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2096,46 +2292,46 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3">
-        <v>9357</v>
-      </c>
+      <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>14126</v>
-      </c>
-      <c r="S18" s="3"/>
+        <v>297580</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2143,21 +2339,17 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026030082</v>
+        <v>2026030517</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2166,46 +2358,44 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>106</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="M19" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="N19" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="N19" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="O19" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>119830</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>297580</v>
+      </c>
+      <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2213,7 +2403,7 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
@@ -2223,7 +2413,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026030083</v>
+        <v>2026030138</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2232,34 +2422,34 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>43</v>
@@ -2267,7 +2457,7 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>119830</v>
+        <v>26945</v>
       </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2277,19 +2467,21 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB20" s="3"/>
+      <c r="AB20" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026030131</v>
+        <v>2026030137</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2298,34 +2490,34 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O21" s="7" t="s">
         <v>40</v>
@@ -2333,7 +2525,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>23535</v>
+        <v>26945</v>
       </c>
       <c r="S21" s="7" t="s">
         <v>41</v>
@@ -2345,9 +2537,11 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA21" s="7"/>
+        <v>110</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB21" s="7"/>
     </row>
     <row r="22" spans="1:28">
@@ -2355,7 +2549,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026030132</v>
+        <v>2026030099</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2364,44 +2558,44 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>23535</v>
-      </c>
-      <c r="S22" s="3"/>
+        <v>33400</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -2409,19 +2603,21 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB22" s="3"/>
+      <c r="AB22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026030084</v>
+        <v>2026030100</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2430,46 +2626,42 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>119</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>33400</v>
+      </c>
+      <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -2477,9 +2669,11 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA23" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB23" s="7"/>
     </row>
     <row r="24" spans="1:28">
@@ -2487,7 +2681,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026030085</v>
+        <v>2026030519</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2496,34 +2690,34 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="N24" s="6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>43</v>
@@ -2531,7 +2725,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>130600</v>
+        <v>82350</v>
       </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2541,11 +2735,9 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
@@ -2553,7 +2745,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026030086</v>
+        <v>2026030518</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2562,44 +2754,46 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="M25" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="N25" s="8" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S25" s="7"/>
+        <v>82350</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -2607,11 +2801,9 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
@@ -2619,7 +2811,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026030090</v>
+        <v>2026030128</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2628,38 +2820,44 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L26" s="6" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3">
+        <v>2829</v>
+      </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>347619</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>41</v>
@@ -2669,11 +2867,9 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
@@ -2687,7 +2883,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026030344</v>
+        <v>2026030129</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2696,66 +2892,66 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="I27" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="J27" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
+      <c r="K27" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L27" s="8" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="Q27" s="7">
+        <v>2829</v>
+      </c>
       <c r="R27" s="7">
-        <v>0</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>347619</v>
+      </c>
+      <c r="S27" s="7"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB27" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026030002</v>
+        <v>2026030489</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -2764,37 +2960,33 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="N28" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="O28" s="3" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -2802,14 +2994,16 @@
         <v>0</v>
       </c>
       <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
+      <c r="T28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>41</v>
@@ -2823,7 +3017,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026030092</v>
+        <v>2026030490</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -2832,30 +3026,30 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="O29" s="7" t="s">
         <v>40</v>
@@ -2873,11 +3067,9 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>41</v>
@@ -2891,7 +3083,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026030094</v>
+        <v>2026030010</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -2900,38 +3092,44 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L30" s="6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="3">
+        <v>335</v>
+      </c>
       <c r="R30" s="3">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>41</v>
@@ -2941,51 +3139,1863 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
+      <c r="A31" s="7">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7">
+        <v>2026030011</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7">
+        <v>335</v>
+      </c>
+      <c r="R31" s="7">
+        <v>2883</v>
+      </c>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB31" s="7"/>
+    </row>
+    <row r="32" spans="1:28">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2026030118</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="AA30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="9" t="s">
+      <c r="O32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3">
+        <v>9357</v>
+      </c>
+      <c r="R32" s="3">
+        <v>14126</v>
+      </c>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="AB31" s="9">
-        <v>15</v>
+      <c r="AA32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28">
+      <c r="A33" s="7">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2026030427</v>
+      </c>
+      <c r="C33" s="7">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7">
+        <v>52012</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB33" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2026030428</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3">
+        <v>52012</v>
+      </c>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB34" s="3"/>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35" s="7">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7">
+        <v>2026030414</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7">
+        <v>84285</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2026030415</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3">
+        <v>84285</v>
+      </c>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB36" s="3"/>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37" s="7">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2026030412</v>
+      </c>
+      <c r="C37" s="7">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7">
+        <v>6105</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2026030413</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3">
+        <v>6105</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38" s="3"/>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="A39" s="7">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2026030082</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7">
+        <v>119830</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
+    </row>
+    <row r="40" spans="1:28">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2026030083</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3">
+        <v>119830</v>
+      </c>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="7">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2026030131</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7">
+        <v>23535</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2026030132</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3">
+        <v>23535</v>
+      </c>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB42" s="3"/>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="A43" s="7">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7">
+        <v>2026030472</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7">
+        <v>14817</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2026030473</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3">
+        <v>14817</v>
+      </c>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB44" s="3"/>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="A45" s="7">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2026030477</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7">
+        <v>58626</v>
+      </c>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2026030476</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3">
+        <v>58626</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="A47" s="7">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7">
+        <v>2026030084</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2026030085</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3">
+        <v>130600</v>
+      </c>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB48" s="3"/>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="A49" s="7">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7">
+        <v>2026030086</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB49" s="7"/>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>2026030474</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3">
+        <v>98716</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3"/>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="A51" s="7">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2026030475</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7">
+        <v>98716</v>
+      </c>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB51" s="7"/>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2026030090</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="A53" s="7">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7">
+        <v>2026030287</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2026030344</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="A55" s="7">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7">
+        <v>2026030002</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7">
+        <v>0</v>
+      </c>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2026030092</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3">
+        <v>0</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z56" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="A57" s="7">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7">
+        <v>2026030094</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7">
+        <v>0</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z57" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB57" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
+      <c r="S58" s="9"/>
+      <c r="T58" s="9"/>
+      <c r="U58" s="9"/>
+      <c r="V58" s="9"/>
+      <c r="W58" s="9"/>
+      <c r="X58" s="9"/>
+      <c r="Y58" s="9"/>
+      <c r="Z58" s="10"/>
+      <c r="AA58" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202603_Service_Count_Report.xlsx
+++ b/IM/202603_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$101</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="349">
   <si>
     <t>服務次數統計表        篩選月份：202603</t>
   </si>
@@ -125,6 +125,60 @@
     <t>劉柏均</t>
   </si>
   <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>13:32:00</t>
+  </si>
+  <si>
+    <t>14:01:00</t>
+  </si>
+  <si>
+    <t>T250A00043</t>
+  </si>
+  <si>
+    <t>eS-2500AC 彩色複合機</t>
+  </si>
+  <si>
+    <t>MFP商品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">力貫國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區連城路258號12樓之8</t>
+  </si>
+  <si>
+    <t>服務</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Pm 到廢粉</t>
+  </si>
+  <si>
+    <t>09:50:00</t>
+  </si>
+  <si>
+    <t>10:16:00</t>
+  </si>
+  <si>
+    <t>T252000054</t>
+  </si>
+  <si>
+    <t>eS-2520AC 彩色複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佳諾金屬有限公司 </t>
+  </si>
+  <si>
+    <t>新北市永和區中和路343號17樓</t>
+  </si>
+  <si>
+    <t>Pm 到廢粉 k要補</t>
+  </si>
+  <si>
     <t>2026-03-02</t>
   </si>
   <si>
@@ -137,12 +191,6 @@
     <t>T252000089</t>
   </si>
   <si>
-    <t>eS-2520AC 彩色複合機</t>
-  </si>
-  <si>
-    <t>MFP商品</t>
-  </si>
-  <si>
     <t xml:space="preserve">漢庭營造股份有限公司 </t>
   </si>
   <si>
@@ -152,12 +200,6 @@
     <t>中和</t>
   </si>
   <si>
-    <t>服務</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
     <t>Pm 灌區動</t>
   </si>
   <si>
@@ -236,6 +278,33 @@
     <t>列印教學</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:45:00</t>
+  </si>
+  <si>
+    <t>T352800007</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建二路56號</t>
+  </si>
+  <si>
+    <t>1 4 紙夾互換 測試紙夾偵測正常</t>
+  </si>
+  <si>
+    <t>11:32:00</t>
+  </si>
+  <si>
+    <t>Pm</t>
+  </si>
+  <si>
     <t>14:30:00</t>
   </si>
   <si>
@@ -275,6 +344,24 @@
     <t>PMQ1 7210002765</t>
   </si>
   <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>10:43:00</t>
+  </si>
+  <si>
+    <t>THILF02398</t>
+  </si>
+  <si>
+    <t>新北市中和區泰和街10號</t>
+  </si>
+  <si>
+    <t>中和泰和店</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L90</t>
+  </si>
+  <si>
     <t>11:40:00</t>
   </si>
   <si>
@@ -290,7 +377,19 @@
     <t>中和自治店</t>
   </si>
   <si>
-    <t xml:space="preserve"> L90</t>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>THILF04101</t>
+  </si>
+  <si>
+    <t>新北市三重區溪尾街293號及295號</t>
+  </si>
+  <si>
+    <t>三重溪華店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002789</t>
   </si>
   <si>
     <t>15:25:00</t>
@@ -326,7 +425,43 @@
     <t>中和霸氣店</t>
   </si>
   <si>
-    <t>09:50:00</t>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
+  </si>
+  <si>
+    <t>THILF04970</t>
+  </si>
+  <si>
+    <t>新北市中和區宜安路36、38號</t>
+  </si>
+  <si>
+    <t>中和一品苑</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:32:00</t>
+  </si>
+  <si>
+    <t>THILF05316</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街209號1樓及地下室</t>
+  </si>
+  <si>
+    <t>三重五常店</t>
+  </si>
+  <si>
+    <t>更換 vga線</t>
   </si>
   <si>
     <t>10:09:00</t>
@@ -341,9 +476,63 @@
     <t>北縣福美店</t>
   </si>
   <si>
+    <t>12:03:00</t>
+  </si>
+  <si>
+    <t>12:23:00</t>
+  </si>
+  <si>
+    <t>THILF0C894</t>
+  </si>
+  <si>
+    <t>新北市中和區建八路116號</t>
+  </si>
+  <si>
+    <t>中和遠東店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002984 L90</t>
+  </si>
+  <si>
     <t>吳宗鴻</t>
   </si>
   <si>
+    <t>12:07:00</t>
+  </si>
+  <si>
+    <t>T252000025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">品興營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市泰山區莊田路與信華三街交叉口(華固一莊)</t>
+  </si>
+  <si>
+    <t>華固一莊</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>T252000125</t>
+  </si>
+  <si>
+    <t>合作金庫商業銀行股份有限公司林口文化分行</t>
+  </si>
+  <si>
+    <t>新北市林口區文化二路1段62-5號2F(放款部</t>
+  </si>
+  <si>
+    <t>林口文化2F放款部</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
     <t>14:49:00</t>
   </si>
   <si>
@@ -362,9 +551,6 @@
     <t>林口長庚分行</t>
   </si>
   <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
     <t>14:16:00</t>
   </si>
   <si>
@@ -381,9 +567,6 @@
   </si>
   <si>
     <t>淡水</t>
-  </si>
-  <si>
-    <t>09:30:00</t>
   </si>
   <si>
     <t>12:00:00</t>
@@ -406,9 +589,6 @@
     <t>14:50:00</t>
   </si>
   <si>
-    <t>15:40:00</t>
-  </si>
-  <si>
     <t>T302800131</t>
   </si>
   <si>
@@ -428,6 +608,93 @@
   </si>
   <si>
     <t>新北市淡水區中正路28號4樓(淡水)</t>
+  </si>
+  <si>
+    <t>10:55:00</t>
+  </si>
+  <si>
+    <t>T452800047</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> eS-4528A 黑白複合機</t>
+  </si>
+  <si>
+    <t>新北市林口區文化二路1段62-5號1F(營業部)</t>
+  </si>
+  <si>
+    <t>林口文化1F營業部</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
+    <t>THILF02763</t>
+  </si>
+  <si>
+    <t>桃園市龜山區頂湖23號、頂湖三街2號</t>
+  </si>
+  <si>
+    <t>桃縣桃燿店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002700 L90</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>11:52:00</t>
+  </si>
+  <si>
+    <t>THILF03692</t>
+  </si>
+  <si>
+    <t>桃園市龜山區頂湖路1號</t>
+  </si>
+  <si>
+    <t>龜山頂湖店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002703 L90</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>THILF04629</t>
+  </si>
+  <si>
+    <t>桃園市龜山區樹人路56號</t>
+  </si>
+  <si>
+    <t>龜山警大店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002708</t>
+  </si>
+  <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>THILF04933</t>
+  </si>
+  <si>
+    <t>桃園市龜山區萬壽路一段388、390號</t>
+  </si>
+  <si>
+    <t>龜山連莊店</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002712 L90</t>
   </si>
   <si>
     <t>11:00:00</t>
@@ -473,9 +740,6 @@
     <t>13:00:00</t>
   </si>
   <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
     <t>T252000143</t>
   </si>
   <si>
@@ -491,7 +755,19 @@
     <t>白線 清潔雷射頭</t>
   </si>
   <si>
-    <t>10:00:00</t>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>T301800026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永佳樂有線電視股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市泰山區美寧街57巷34號1樓(異地備援)</t>
+  </si>
+  <si>
+    <t>異地備援泰山</t>
   </si>
   <si>
     <t>T301800171</t>
@@ -512,12 +788,87 @@
     <t>板橋</t>
   </si>
   <si>
+    <t>T302800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">財團法人台灣省私立台灣盲人重建院 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號3樓</t>
+  </si>
+  <si>
+    <t>3F</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>新電腦設定驅動掃描</t>
+  </si>
+  <si>
+    <t>T302800008</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號4樓</t>
+  </si>
+  <si>
+    <t>4F</t>
+  </si>
+  <si>
     <t>T302800123</t>
   </si>
   <si>
     <t>新北市三重區正義北路218號(三重分校)</t>
   </si>
   <si>
+    <t>T302800152</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(營管部)</t>
+  </si>
+  <si>
+    <t>營管部</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>T302800153</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(走道)</t>
+  </si>
+  <si>
+    <t>走道</t>
+  </si>
+  <si>
+    <t>16:40:00</t>
+  </si>
+  <si>
+    <t>T302800154</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(櫃台2)</t>
+  </si>
+  <si>
+    <t>櫃台2</t>
+  </si>
+  <si>
+    <t>T302800155</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(工程部2)</t>
+  </si>
+  <si>
+    <t>工程部2</t>
+  </si>
+  <si>
+    <t>T302800156</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(工程部1)</t>
+  </si>
+  <si>
     <t>T351800045</t>
   </si>
   <si>
@@ -533,12 +884,27 @@
     <t>五股生鮮物流</t>
   </si>
   <si>
+    <t>T351800082</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(櫃台1)</t>
+  </si>
+  <si>
+    <t>櫃台1</t>
+  </si>
+  <si>
+    <t>T351800085</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路651-5號10樓(節目部)</t>
+  </si>
+  <si>
+    <t>節目部</t>
+  </si>
+  <si>
     <t>T352800011</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">全聯實業股份有限公司 </t>
   </si>
   <si>
@@ -584,6 +950,9 @@
     <t>髒汙 更換上熱</t>
   </si>
   <si>
+    <t>更換上熱 雷射</t>
+  </si>
+  <si>
     <t>T352800032</t>
   </si>
   <si>
@@ -593,9 +962,6 @@
     <t>五股運輸</t>
   </si>
   <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
     <t>THILF02325</t>
   </si>
   <si>
@@ -612,12 +978,6 @@
   </si>
   <si>
     <t>THILF02749</t>
-  </si>
-  <si>
-    <t>一般件</t>
-  </si>
-  <si>
-    <t>其他</t>
   </si>
   <si>
     <t>新北市淡水區淡金路5段20-22號</t>
@@ -661,6 +1021,21 @@
     <t>清潔發票機 重接排線</t>
   </si>
   <si>
+    <t>THILF04316</t>
+  </si>
+  <si>
+    <t>新北市五股區成泰路二段91巷9號1樓部份</t>
+  </si>
+  <si>
+    <t>五股工商店</t>
+  </si>
+  <si>
+    <t>更換SC螢幕，SC測試撥放音效正常
+監視器仍異常，請門市報修監視器廠商
+換上8133003307
+換下8133002431</t>
+  </si>
+  <si>
     <t>THILF04801</t>
   </si>
   <si>
@@ -689,6 +1064,24 @@
   </si>
   <si>
     <t>PMQ1 7210002835 L90</t>
+  </si>
+  <si>
+    <t>狄澤洋</t>
+  </si>
+  <si>
+    <t>13:12:00</t>
+  </si>
+  <si>
+    <t>THILF0D111</t>
+  </si>
+  <si>
+    <t>新北市板橋區府中路24號</t>
+  </si>
+  <si>
+    <t>板橋府中店</t>
+  </si>
+  <si>
+    <t>線路重新插拔，驅動校正後測試正常</t>
   </si>
   <si>
     <t>合計</t>
@@ -1105,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1261,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7">
-        <v>2026030035</v>
+        <v>2026030711</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -1296,21 +1689,19 @@
       <c r="M3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="8"/>
+      <c r="O3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7">
-        <v>3658</v>
+        <v>23489</v>
       </c>
       <c r="R3" s="7">
-        <v>16773</v>
+        <v>87335</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -1319,10 +1710,10 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB3" s="7">
         <v>1</v>
@@ -1333,7 +1724,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2026030036</v>
+        <v>2026030627</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1348,40 +1739,40 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3">
-        <v>3658</v>
+        <v>1303</v>
       </c>
       <c r="R4" s="3">
-        <v>16773</v>
-      </c>
-      <c r="S4" s="3"/>
+        <v>17655</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1389,19 +1780,21 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB4" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026030325</v>
+        <v>2026030035</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1413,43 +1806,45 @@
         <v>30</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="N5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7">
-        <v>3664</v>
+        <v>3658</v>
       </c>
       <c r="R5" s="7">
-        <v>16787</v>
-      </c>
-      <c r="S5" s="7"/>
+        <v>16773</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -1457,10 +1852,10 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB5" s="7">
         <v>1</v>
@@ -1471,7 +1866,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026030080</v>
+        <v>2026030036</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1483,45 +1878,43 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3">
-        <v>914</v>
+        <v>3658</v>
       </c>
       <c r="R6" s="3">
-        <v>1163</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>16773</v>
+      </c>
+      <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1529,21 +1922,19 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB6" s="3"/>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026030081</v>
+        <v>2026030325</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1555,41 +1946,41 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7">
-        <v>914</v>
+        <v>3664</v>
       </c>
       <c r="R7" s="7">
-        <v>1163</v>
+        <v>16787</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -1599,19 +1990,21 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB7" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026030436</v>
+        <v>2026030080</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1623,42 +2016,44 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="3">
+        <v>914</v>
+      </c>
       <c r="R8" s="3">
-        <v>282084</v>
+        <v>1163</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -1667,10 +2062,10 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB8" s="3">
         <v>1</v>
@@ -1681,7 +2076,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026030437</v>
+        <v>2026030081</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1693,39 +2088,41 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
+      <c r="Q9" s="7">
+        <v>914</v>
+      </c>
       <c r="R9" s="7">
-        <v>282084</v>
+        <v>1163</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -1735,10 +2132,10 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB9" s="7"/>
     </row>
@@ -1747,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026030443</v>
+        <v>2026030436</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1759,42 +2156,42 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>31261</v>
+        <v>282084</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -1803,10 +2200,10 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB10" s="3">
         <v>1</v>
@@ -1817,7 +2214,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026030444</v>
+        <v>2026030437</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1829,39 +2226,39 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>31261</v>
+        <v>282084</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -1871,10 +2268,10 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB11" s="7"/>
     </row>
@@ -1883,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026030300</v>
+        <v>2026030443</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1895,50 +2292,54 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L12" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>31261</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB12" s="3">
         <v>1</v>
@@ -1949,7 +2350,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026030328</v>
+        <v>2026030444</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1961,10 +2362,10 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>76</v>
@@ -1972,52 +2373,50 @@
       <c r="I13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L13" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>0</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>31261</v>
+      </c>
+      <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB13" s="7">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB13" s="7"/>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026030460</v>
+        <v>2026030536</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2029,39 +2428,39 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L14" s="6" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>215118</v>
+      </c>
+      <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -2069,10 +2468,10 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB14" s="3">
         <v>1</v>
@@ -2083,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026030316</v>
+        <v>2026030690</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2098,49 +2497,49 @@
         <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>91</v>
-      </c>
+      <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>0</v>
+        <v>215118</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB15" s="7">
         <v>1</v>
@@ -2151,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026030450</v>
+        <v>2026030691</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2163,39 +2562,39 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L16" s="6" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N16" s="6"/>
       <c r="O16" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>215118</v>
+      </c>
+      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2203,21 +2602,19 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB16" s="3"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026030423</v>
+        <v>2026030300</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2229,50 +2626,50 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
         <v>0</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AA17" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB17" s="7">
         <v>1</v>
@@ -2283,7 +2680,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026030516</v>
+        <v>2026030328</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2292,64 +2689,66 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>297580</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026030517</v>
+        <v>2026030635</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2358,10 +2757,10 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>104</v>
@@ -2372,30 +2771,28 @@
       <c r="I19" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M19" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="N19" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="N19" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="O19" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>297580</v>
-      </c>
-      <c r="S19" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2403,17 +2800,21 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
+        <v>109</v>
+      </c>
+      <c r="AA19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026030138</v>
+        <v>2026030460</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2422,44 +2823,42 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" s="6" t="s">
+      <c r="N20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="M20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="O20" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>26945</v>
-      </c>
-      <c r="S20" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -2467,10 +2866,10 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB20" s="3">
         <v>1</v>
@@ -2481,7 +2880,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026030137</v>
+        <v>2026030867</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2490,66 +2889,66 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>26945</v>
+        <v>0</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z21" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AA21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB21" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026030099</v>
+        <v>2026030316</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2558,55 +2957,55 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="6" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="N22" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="O22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>33400</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
+      <c r="Y22" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z22" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB22" s="3">
         <v>1</v>
@@ -2617,7 +3016,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026030100</v>
+        <v>2026030450</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2626,42 +3025,42 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="N23" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="O23" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7">
-        <v>33400</v>
-      </c>
-      <c r="S23" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -2669,19 +3068,21 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB23" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026030519</v>
+        <v>2026030583</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2690,44 +3091,42 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
       <c r="L24" s="6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>82350</v>
-      </c>
-      <c r="S24" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2735,17 +3134,21 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026030518</v>
+        <v>2026030684</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2754,46 +3157,44 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>82350</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -2801,17 +3202,21 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
+        <v>143</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026030128</v>
+        <v>2026030423</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2820,47 +3225,41 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
       <c r="L26" s="6" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3">
-        <v>2829</v>
-      </c>
+      <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>347619</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -2869,10 +3268,10 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB26" s="3">
         <v>1</v>
@@ -2883,7 +3282,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026030129</v>
+        <v>2026030694</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2892,66 +3291,66 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7">
-        <v>2829</v>
-      </c>
+      <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>347619</v>
-      </c>
-      <c r="S27" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
+      <c r="Y27" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z27" s="8" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="AA27" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB27" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB27" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026030489</v>
+        <v>2026030689</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -2960,53 +3359,59 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L28" s="6" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="P28" s="3">
+        <v>7527</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>16471</v>
+      </c>
       <c r="R28" s="3">
-        <v>0</v>
+        <v>23071</v>
       </c>
       <c r="S28" s="3"/>
-      <c r="T28" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB28" s="3">
         <v>1</v>
@@ -3017,7 +3422,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026030490</v>
+        <v>2026030678</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3026,41 +3431,47 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
+        <v>162</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L29" s="8" t="s">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="Q29" s="7">
+        <v>1705</v>
+      </c>
       <c r="R29" s="7">
-        <v>0</v>
+        <v>93726</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
@@ -3069,21 +3480,17 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB29" s="7">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA29" s="7"/>
+      <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026030010</v>
+        <v>2026030679</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3092,48 +3499,46 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3">
-        <v>335</v>
+        <v>1705</v>
       </c>
       <c r="R30" s="3">
-        <v>2883</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>93726</v>
+      </c>
+      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -3141,21 +3546,17 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026030011</v>
+        <v>2026030516</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3164,46 +3565,46 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P31" s="7"/>
-      <c r="Q31" s="7">
-        <v>335</v>
-      </c>
+      <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>2883</v>
-      </c>
-      <c r="S31" s="7"/>
+        <v>297580</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -3211,11 +3612,9 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:28">
@@ -3223,7 +3622,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026030118</v>
+        <v>2026030517</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3232,44 +3631,42 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3">
-        <v>9357</v>
-      </c>
+      <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>14126</v>
+        <v>297580</v>
       </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
@@ -3279,21 +3676,17 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026030427</v>
+        <v>2026030137</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3302,45 +3695,45 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>52012</v>
+        <v>26945</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -3349,10 +3742,10 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="AA33" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB33" s="7">
         <v>1</v>
@@ -3363,7 +3756,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026030428</v>
+        <v>2026030138</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3372,42 +3765,42 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>52012</v>
+        <v>26945</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3417,10 +3810,10 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB34" s="3"/>
     </row>
@@ -3429,7 +3822,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026030414</v>
+        <v>2026030099</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3438,45 +3831,43 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>158</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N35" s="8"/>
       <c r="O35" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>84285</v>
+        <v>33400</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -3485,10 +3876,10 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="AA35" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB35" s="7">
         <v>1</v>
@@ -3499,7 +3890,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026030415</v>
+        <v>2026030100</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3508,42 +3899,40 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>158</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N36" s="6"/>
       <c r="O36" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>84285</v>
+        <v>33400</v>
       </c>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
@@ -3553,10 +3942,10 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB36" s="3"/>
     </row>
@@ -3565,7 +3954,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026030412</v>
+        <v>2026030518</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3574,45 +3963,45 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>6105</v>
+        <v>82350</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
@@ -3621,21 +4010,17 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB37" s="7">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026030413</v>
+        <v>2026030519</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3644,42 +4029,42 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3">
-        <v>6105</v>
+        <v>82350</v>
       </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
@@ -3689,11 +4074,9 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA38" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
@@ -3701,7 +4084,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026030082</v>
+        <v>2026030128</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3710,45 +4093,47 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="Q39" s="7">
+        <v>2829</v>
+      </c>
       <c r="R39" s="7">
-        <v>119830</v>
+        <v>347619</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -3757,17 +4142,21 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA39" s="7"/>
-      <c r="AB39" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="AA39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:28">
       <c r="A40" s="3">
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026030083</v>
+        <v>2026030129</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3776,42 +4165,44 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
+      <c r="Q40" s="3">
+        <v>2829</v>
+      </c>
       <c r="R40" s="3">
-        <v>119830</v>
+        <v>347619</v>
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -3821,10 +4212,10 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB40" s="3"/>
     </row>
@@ -3833,7 +4224,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026030131</v>
+        <v>2026030680</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -3842,45 +4233,45 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>23535</v>
+        <v>158084</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
@@ -3889,7 +4280,7 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="AA41" s="7"/>
       <c r="AB41" s="7"/>
@@ -3899,7 +4290,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026030132</v>
+        <v>2026030681</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -3908,42 +4299,42 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>23535</v>
+        <v>158084</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -3953,11 +4344,9 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
@@ -3965,7 +4354,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026030472</v>
+        <v>2026030705</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -3974,45 +4363,41 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
       <c r="L43" s="8" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>14817</v>
+        <v>0</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
@@ -4021,17 +4406,21 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
+        <v>202</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB43" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026030473</v>
+        <v>2026030686</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4040,44 +4429,42 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
       <c r="L44" s="6" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>14817</v>
-      </c>
-      <c r="S44" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -4085,19 +4472,21 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>144</v>
+        <v>208</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB44" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="7">
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026030477</v>
+        <v>2026030718</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4106,44 +4495,42 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
       <c r="L45" s="8" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>58626</v>
-      </c>
-      <c r="S45" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
@@ -4151,10 +4538,10 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="AA45" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB45" s="7">
         <v>1</v>
@@ -4165,7 +4552,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026030476</v>
+        <v>2026030740</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4174,45 +4561,41 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
       <c r="L46" s="6" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>58626</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
@@ -4221,17 +4604,21 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026030084</v>
+        <v>2026030489</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4240,64 +4627,64 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
       <c r="L47" s="8" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T47" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
+        <v>225</v>
+      </c>
+      <c r="AA47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB47" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026030085</v>
+        <v>2026030490</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4306,44 +4693,42 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
       <c r="L48" s="6" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3">
-        <v>130600</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4351,19 +4736,21 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB48" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:28">
       <c r="A49" s="7">
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026030086</v>
+        <v>2026030010</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4372,44 +4759,48 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>335</v>
+      </c>
       <c r="R49" s="7">
-        <v>130600</v>
-      </c>
-      <c r="S49" s="7"/>
+        <v>2883</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
@@ -4417,19 +4808,21 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="AA49" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB49" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026030474</v>
+        <v>2026030011</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4438,46 +4831,46 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="3">
+        <v>335</v>
+      </c>
       <c r="R50" s="3">
-        <v>98716</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>2883</v>
+      </c>
+      <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4485,9 +4878,11 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA50" s="3"/>
+        <v>233</v>
+      </c>
+      <c r="AA50" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB50" s="3"/>
     </row>
     <row r="51" spans="1:28">
@@ -4495,7 +4890,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026030475</v>
+        <v>2026030118</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4504,42 +4899,44 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
+      <c r="Q51" s="7">
+        <v>9357</v>
+      </c>
       <c r="R51" s="7">
-        <v>98716</v>
+        <v>14126</v>
       </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
@@ -4549,19 +4946,21 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="AA51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB51" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026030090</v>
+        <v>2026030775</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4570,55 +4969,57 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L52" s="6" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>188</v>
+        <v>243</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>1829</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
-      <c r="Y52" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="AA52" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB52" s="3">
         <v>1</v>
@@ -4629,7 +5030,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026030287</v>
+        <v>2026030776</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4638,42 +5039,42 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>0</v>
+        <v>1829</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
@@ -4683,21 +5084,19 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="AA53" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB53" s="7">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB53" s="7"/>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026030344</v>
+        <v>2026030427</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -4706,55 +5105,57 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+        <v>245</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L54" s="6" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>0</v>
+        <v>52012</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
-      <c r="Y54" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="AA54" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB54" s="3">
         <v>1</v>
@@ -4765,7 +5166,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026030002</v>
+        <v>2026030428</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4774,42 +5175,42 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>0</v>
+        <v>52012</v>
       </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
@@ -4819,21 +5220,19 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="AA55" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB55" s="7">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB55" s="7"/>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026030092</v>
+        <v>2026030414</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -4842,55 +5241,57 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
+        <v>248</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L56" s="6" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>0</v>
+        <v>84285</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="AA56" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB56" s="3">
         <v>1</v>
@@ -4901,7 +5302,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026030094</v>
+        <v>2026030415</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -4910,92 +5311,2990 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
+        <v>248</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L57" s="8" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>0</v>
-      </c>
-      <c r="S57" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>84285</v>
+      </c>
+      <c r="S57" s="7"/>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
       <c r="W57" s="7"/>
       <c r="X57" s="7"/>
-      <c r="Y57" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AA57" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB57" s="7">
-        <v>1</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AB57" s="7"/>
     </row>
     <row r="58" spans="1:28">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="9"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="10"/>
-      <c r="AA58" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB58" s="9">
-        <v>28</v>
+      <c r="A58" s="3">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3">
+        <v>2026030602</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3">
+        <v>180909</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="7">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7">
+        <v>2026030603</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7">
+        <v>180909</v>
+      </c>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB59" s="7"/>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3">
+        <v>2026030688</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3">
+        <v>180909</v>
+      </c>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28">
+      <c r="A61" s="7">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7">
+        <v>2026030605</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7">
+        <v>179230</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB61" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28">
+      <c r="A62" s="3">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>2026030606</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3">
+        <v>179230</v>
+      </c>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB62" s="3"/>
+    </row>
+    <row r="63" spans="1:28">
+      <c r="A63" s="7">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <v>2026030412</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="N63" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7">
+        <v>6105</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA63" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28">
+      <c r="A64" s="3">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>2026030413</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3">
+        <v>6105</v>
+      </c>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB64" s="3"/>
+    </row>
+    <row r="65" spans="1:28">
+      <c r="A65" s="7">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <v>2026030772</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="N65" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7">
+        <v>25095</v>
+      </c>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28">
+      <c r="A66" s="3">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3">
+        <v>2026030771</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3">
+        <v>25095</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB66" s="3"/>
+    </row>
+    <row r="67" spans="1:28">
+      <c r="A67" s="7">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7">
+        <v>2026030767</v>
+      </c>
+      <c r="C67" s="7">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="N67" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7">
+        <v>27243</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA67" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB67" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28">
+      <c r="A68" s="3">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3">
+        <v>2026030768</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3">
+        <v>27243</v>
+      </c>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB68" s="3"/>
+    </row>
+    <row r="69" spans="1:28">
+      <c r="A69" s="7">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7">
+        <v>2026030777</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N69" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7">
+        <v>19342</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7"/>
+      <c r="V69" s="7"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA69" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28">
+      <c r="A70" s="3">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3">
+        <v>2026030778</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3">
+        <v>19342</v>
+      </c>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA70" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB70" s="3"/>
+    </row>
+    <row r="71" spans="1:28">
+      <c r="A71" s="7">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7">
+        <v>2026030765</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="N71" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7">
+        <v>23130</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="7"/>
+      <c r="W71" s="7"/>
+      <c r="X71" s="7"/>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28">
+      <c r="A72" s="3">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2026030766</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3">
+        <v>23130</v>
+      </c>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB72" s="3"/>
+    </row>
+    <row r="73" spans="1:28">
+      <c r="A73" s="7">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7">
+        <v>2026030763</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N73" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7">
+        <v>12518</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA73" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB73" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28">
+      <c r="A74" s="3">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2026030764</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3">
+        <v>12518</v>
+      </c>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB74" s="3"/>
+    </row>
+    <row r="75" spans="1:28">
+      <c r="A75" s="7">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7">
+        <v>2026030082</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="N75" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="O75" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7">
+        <v>119830</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="7"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA75" s="7"/>
+      <c r="AB75" s="7"/>
+    </row>
+    <row r="76" spans="1:28">
+      <c r="A76" s="3">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2026030083</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3">
+        <v>119830</v>
+      </c>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB76" s="3"/>
+    </row>
+    <row r="77" spans="1:28">
+      <c r="A77" s="7">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7">
+        <v>2026030773</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="N77" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7">
+        <v>479</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA77" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28">
+      <c r="A78" s="3">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3">
+        <v>2026030774</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3">
+        <v>479</v>
+      </c>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB78" s="3"/>
+    </row>
+    <row r="79" spans="1:28">
+      <c r="A79" s="7">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2026030769</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7">
+        <v>4221</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA79" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB79" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2026030770</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3">
+        <v>4221</v>
+      </c>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB80" s="3"/>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="7">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2026030131</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7">
+        <v>23535</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA81" s="7"/>
+      <c r="AB81" s="7"/>
+    </row>
+    <row r="82" spans="1:28">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2026030132</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3">
+        <v>23535</v>
+      </c>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="1:28">
+      <c r="A83" s="7">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2026030472</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="O83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7">
+        <v>14817</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA83" s="7"/>
+      <c r="AB83" s="7"/>
+    </row>
+    <row r="84" spans="1:28">
+      <c r="A84" s="3">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2026030473</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3">
+        <v>14817</v>
+      </c>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB84" s="3"/>
+    </row>
+    <row r="85" spans="1:28">
+      <c r="A85" s="7">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <v>2026030476</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O85" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7">
+        <v>58626</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T85" s="7"/>
+      <c r="U85" s="7"/>
+      <c r="V85" s="7"/>
+      <c r="W85" s="7"/>
+      <c r="X85" s="7"/>
+      <c r="Y85" s="7"/>
+      <c r="Z85" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA85" s="7"/>
+      <c r="AB85" s="7"/>
+    </row>
+    <row r="86" spans="1:28">
+      <c r="A86" s="3">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2026030477</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3">
+        <v>58626</v>
+      </c>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB86" s="3"/>
+    </row>
+    <row r="87" spans="1:28">
+      <c r="A87" s="7">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <v>2026030084</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="N87" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T87" s="7"/>
+      <c r="U87" s="7"/>
+      <c r="V87" s="7"/>
+      <c r="W87" s="7"/>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="7"/>
+      <c r="Z87" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7"/>
+    </row>
+    <row r="88" spans="1:28">
+      <c r="A88" s="3">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2026030085</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3">
+        <v>130600</v>
+      </c>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB88" s="3"/>
+    </row>
+    <row r="89" spans="1:28">
+      <c r="A89" s="7">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <v>2026030086</v>
+      </c>
+      <c r="C89" s="7">
+        <v>1</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
+      <c r="R89" s="7">
+        <v>130600</v>
+      </c>
+      <c r="S89" s="7"/>
+      <c r="T89" s="7"/>
+      <c r="U89" s="7"/>
+      <c r="V89" s="7"/>
+      <c r="W89" s="7"/>
+      <c r="X89" s="7"/>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA89" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB89" s="7"/>
+    </row>
+    <row r="90" spans="1:28">
+      <c r="A90" s="3">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2026030702</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3">
+        <v>130600</v>
+      </c>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z90" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="AA90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28">
+      <c r="A91" s="7">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7">
+        <v>2026030474</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="N91" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="O91" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7">
+        <v>98716</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T91" s="7"/>
+      <c r="U91" s="7"/>
+      <c r="V91" s="7"/>
+      <c r="W91" s="7"/>
+      <c r="X91" s="7"/>
+      <c r="Y91" s="7"/>
+      <c r="Z91" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA91" s="7"/>
+      <c r="AB91" s="7"/>
+    </row>
+    <row r="92" spans="1:28">
+      <c r="A92" s="3">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3">
+        <v>2026030475</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3">
+        <v>98716</v>
+      </c>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA92" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB92" s="3"/>
+    </row>
+    <row r="93" spans="1:28">
+      <c r="A93" s="7">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7">
+        <v>2026030090</v>
+      </c>
+      <c r="C93" s="7">
+        <v>1</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="N93" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="O93" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7">
+        <v>0</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T93" s="7"/>
+      <c r="U93" s="7"/>
+      <c r="V93" s="7"/>
+      <c r="W93" s="7"/>
+      <c r="X93" s="7"/>
+      <c r="Y93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z93" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB93" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28">
+      <c r="A94" s="3">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2026030287</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28">
+      <c r="A95" s="7">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7">
+        <v>2026030344</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="N95" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7">
+        <v>0</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T95" s="7"/>
+      <c r="U95" s="7"/>
+      <c r="V95" s="7"/>
+      <c r="W95" s="7"/>
+      <c r="X95" s="7"/>
+      <c r="Y95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z95" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA95" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB95" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28">
+      <c r="A96" s="3">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2026030002</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28">
+      <c r="A97" s="7">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7">
+        <v>2026030458</v>
+      </c>
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="N97" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="O97" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7">
+        <v>0</v>
+      </c>
+      <c r="S97" s="7"/>
+      <c r="T97" s="7"/>
+      <c r="U97" s="7"/>
+      <c r="V97" s="7"/>
+      <c r="W97" s="7"/>
+      <c r="X97" s="7"/>
+      <c r="Y97" s="7"/>
+      <c r="Z97" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA97" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="3">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2026030092</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z98" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="AA98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28">
+      <c r="A99" s="7">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7">
+        <v>2026030094</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="N99" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="7">
+        <v>0</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T99" s="7"/>
+      <c r="U99" s="7"/>
+      <c r="V99" s="7"/>
+      <c r="W99" s="7"/>
+      <c r="X99" s="7"/>
+      <c r="Y99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z99" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="AA99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB99" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28">
+      <c r="A100" s="3">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2026030431</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
+      <c r="Z100" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="10"/>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10"/>
+      <c r="O101" s="9"/>
+      <c r="P101" s="9"/>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
+      <c r="S101" s="9"/>
+      <c r="T101" s="9"/>
+      <c r="U101" s="9"/>
+      <c r="V101" s="9"/>
+      <c r="W101" s="9"/>
+      <c r="X101" s="9"/>
+      <c r="Y101" s="9"/>
+      <c r="Z101" s="10"/>
+      <c r="AA101" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="AB101" s="9">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
